--- a/tests/tiny_hrsa_ahrf_techdoc.xlsx
+++ b/tests/tiny_hrsa_ahrf_techdoc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,47 +1156,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>md_nf_23</t>
+          <t>cnty_name_st_abbrev</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2023</v>
+          <t>GEO</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Total M.D.'s, Total Non-Fed</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Non-Fed;Incl Inact/Not Class</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> County Name w/State Abbrev</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AMA Phys Master File</t>
+          <t xml:space="preserve"> Derived From GSA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>07/25</t>
+          <t>04/81</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hosp_23</t>
+          <t>md_nf_23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HF</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1204,16 +1197,51 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Total M.D.'s, Total Non-Fed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Non-Fed;Incl Inact/Not Class</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> AMA Phys Master File</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>07/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>hosp_23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t xml:space="preserve"> Total Number Hospitals</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve"> AHA Survey Database 23</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>07/25</t>
         </is>
